--- a/research/traditional_assets/database/data/denmark/denmark_education.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_education.xlsx
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.3571207430340557</v>
+        <v>0.00234375</v>
       </c>
       <c r="H2">
-        <v>-0.3730650154798762</v>
+        <v>-0.002864583333333334</v>
       </c>
       <c r="I2">
-        <v>-0.2321981424148607</v>
+        <v>-0.02348958333333333</v>
       </c>
       <c r="J2">
-        <v>-0.2321981424148607</v>
+        <v>-0.02348958333333333</v>
       </c>
       <c r="K2">
-        <v>-1.91</v>
+        <v>-1.13</v>
       </c>
       <c r="L2">
-        <v>-0.2956656346749226</v>
+        <v>-0.05885416666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.521</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.008444084278768233</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>-0.461061946902655</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,76 +624,79 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.521</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>0.123</v>
+        <v>1.16</v>
       </c>
       <c r="V2">
-        <v>0.003121827411167513</v>
+        <v>0.01880064829821718</v>
       </c>
       <c r="W2">
-        <v>-0.6241830065359477</v>
+        <v>-1.097087378640777</v>
       </c>
       <c r="X2">
-        <v>0.09009426979061089</v>
+        <v>0.07649683717487536</v>
       </c>
       <c r="Y2">
-        <v>-0.7142772763265586</v>
+        <v>-1.173584215815652</v>
       </c>
       <c r="Z2">
-        <v>4.141025641025641</v>
+        <v>4.01841774801172</v>
       </c>
       <c r="AA2">
-        <v>-0.9615384615384615</v>
+        <v>-0.09439095856006696</v>
       </c>
       <c r="AB2">
-        <v>0.08545220149364081</v>
+        <v>0.072897330049249</v>
       </c>
       <c r="AC2">
-        <v>-1.046990663032102</v>
+        <v>-0.167288288609316</v>
       </c>
       <c r="AD2">
-        <v>4.62</v>
+        <v>7.13</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4.62</v>
+        <v>7.13</v>
       </c>
       <c r="AG2">
-        <v>4.497</v>
+        <v>5.97</v>
       </c>
       <c r="AH2">
-        <v>0.1049522944116311</v>
+        <v>0.1035885515037048</v>
       </c>
       <c r="AI2">
-        <v>0.8176991150442477</v>
+        <v>0.4274580335731415</v>
       </c>
       <c r="AJ2">
-        <v>0.1024443583843998</v>
+        <v>0.08822225506132703</v>
       </c>
       <c r="AK2">
-        <v>0.8136421204993667</v>
+        <v>0.3846649484536083</v>
       </c>
       <c r="AL2">
-        <v>0.227</v>
+        <v>0.435</v>
       </c>
       <c r="AM2">
-        <v>0.227</v>
+        <v>0.435</v>
       </c>
       <c r="AN2">
-        <v>-3.347826086956522</v>
+        <v>35.29702970297029</v>
       </c>
       <c r="AO2">
-        <v>-6.607929515418502</v>
+        <v>-1.036781609195402</v>
       </c>
       <c r="AP2">
-        <v>-3.258695652173913</v>
+        <v>29.55445544554455</v>
       </c>
       <c r="AQ2">
-        <v>-6.607929515418502</v>
+        <v>-1.036781609195402</v>
       </c>
     </row>
     <row r="3">
@@ -713,31 +716,31 @@
         </is>
       </c>
       <c r="G3">
-        <v>-0.3571207430340557</v>
+        <v>0.00234375</v>
       </c>
       <c r="H3">
-        <v>-0.3730650154798762</v>
+        <v>-0.002864583333333334</v>
       </c>
       <c r="I3">
-        <v>-0.2321981424148607</v>
+        <v>-0.02348958333333333</v>
       </c>
       <c r="J3">
-        <v>-0.2321981424148607</v>
+        <v>-0.02348958333333333</v>
       </c>
       <c r="K3">
-        <v>-1.91</v>
+        <v>-1.13</v>
       </c>
       <c r="L3">
-        <v>-0.2956656346749226</v>
+        <v>-0.05885416666666667</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.521</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.008444084278768233</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0.461061946902655</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -749,76 +752,79 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.521</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>0.123</v>
+        <v>1.16</v>
       </c>
       <c r="V3">
-        <v>0.003121827411167513</v>
+        <v>0.01880064829821718</v>
       </c>
       <c r="W3">
-        <v>-0.6241830065359477</v>
+        <v>-1.097087378640777</v>
       </c>
       <c r="X3">
-        <v>0.09009426979061089</v>
+        <v>0.07649683717487536</v>
       </c>
       <c r="Y3">
-        <v>-0.7142772763265586</v>
+        <v>-1.173584215815652</v>
       </c>
       <c r="Z3">
-        <v>4.141025641025641</v>
+        <v>4.01841774801172</v>
       </c>
       <c r="AA3">
-        <v>-0.9615384615384615</v>
+        <v>-0.09439095856006696</v>
       </c>
       <c r="AB3">
-        <v>0.08545220149364081</v>
+        <v>0.072897330049249</v>
       </c>
       <c r="AC3">
-        <v>-1.046990663032102</v>
+        <v>-0.167288288609316</v>
       </c>
       <c r="AD3">
-        <v>4.62</v>
+        <v>7.13</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>4.62</v>
+        <v>7.13</v>
       </c>
       <c r="AG3">
-        <v>4.497</v>
+        <v>5.97</v>
       </c>
       <c r="AH3">
-        <v>0.1049522944116311</v>
+        <v>0.1035885515037048</v>
       </c>
       <c r="AI3">
-        <v>0.8176991150442477</v>
+        <v>0.4274580335731415</v>
       </c>
       <c r="AJ3">
-        <v>0.1024443583843998</v>
+        <v>0.08822225506132703</v>
       </c>
       <c r="AK3">
-        <v>0.8136421204993667</v>
+        <v>0.3846649484536083</v>
       </c>
       <c r="AL3">
-        <v>0.227</v>
+        <v>0.435</v>
       </c>
       <c r="AM3">
-        <v>0.227</v>
+        <v>0.435</v>
       </c>
       <c r="AN3">
-        <v>-3.347826086956522</v>
+        <v>35.29702970297029</v>
       </c>
       <c r="AO3">
-        <v>-6.607929515418502</v>
+        <v>-1.036781609195402</v>
       </c>
       <c r="AP3">
-        <v>-3.258695652173913</v>
+        <v>29.55445544554455</v>
       </c>
       <c r="AQ3">
-        <v>-6.607929515418502</v>
+        <v>-1.036781609195402</v>
       </c>
     </row>
   </sheetData>
